--- a/outputs/sta332-schedule/sta332-f26-schedule-updated.xlsx
+++ b/outputs/sta332-schedule/sta332-f26-schedule-updated.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabellenblatt1" sheetId="1" r:id="Rb478091088b14e1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabellenblatt1" sheetId="1" r:id="Re9f8ff961da1419e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="6">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="10"/>
       <x:color rgb="FF000000"/>
@@ -45,8 +45,14 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF4A0F63"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -63,14 +69,27 @@
         <x:fgColor rgb="FF5E157D"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE9DDF0"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="1">
+  <x:borders count="2">
     <x:border/>
+    <x:border>
+      <x:top style="medium">
+        <x:color rgb="FF5E157D"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF5E157D"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="18">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0"/>
     </x:xf>
@@ -120,6 +139,42 @@
     </x:xf>
     <x:xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -431,21 +486,21 @@
       <x:c r="I3" s="15"/>
       <x:c r="J3" s="15"/>
     </x:row>
-    <x:row r="4" ht="15.75" hidden="0" customHeight="1">
-      <x:c r="A4" s="16"/>
-      <x:c r="B4" s="16"/>
-      <x:c r="C4" s="17"/>
-      <x:c r="D4" s="16" t="str">
+    <x:row r="4" ht="28" hidden="0" customHeight="1">
+      <x:c r="A4" s="27"/>
+      <x:c r="B4" s="27"/>
+      <x:c r="C4" s="28"/>
+      <x:c r="D4" s="27" t="str">
         <x:v>Section</x:v>
       </x:c>
-      <x:c r="E4" s="16"/>
-      <x:c r="F4" s="15"/>
-      <x:c r="G4" s="15" t="str">
-        <x:v>**Sufficiency and Data Reduction**</x:v>
-      </x:c>
-      <x:c r="H4" s="15"/>
-      <x:c r="I4" s="15"/>
-      <x:c r="J4" s="15"/>
+      <x:c r="E4" s="27"/>
+      <x:c r="F4" s="29"/>
+      <x:c r="G4" s="29" t="str">
+        <x:v>Sufficiency and Data Reduction</x:v>
+      </x:c>
+      <x:c r="H4" s="29"/>
+      <x:c r="I4" s="29"/>
+      <x:c r="J4" s="29"/>
     </x:row>
     <x:row r="5" ht="15.75" hidden="0" customHeight="1">
       <x:c r="A5" s="16" t="n">
@@ -517,21 +572,21 @@
       <x:c r="I7" s="15"/>
       <x:c r="J7" s="15"/>
     </x:row>
-    <x:row r="8" ht="15.75" hidden="0" customHeight="1">
-      <x:c r="A8" s="16"/>
-      <x:c r="B8" s="16"/>
-      <x:c r="C8" s="17"/>
-      <x:c r="D8" s="16" t="str">
+    <x:row r="8" ht="28" hidden="0" customHeight="1">
+      <x:c r="A8" s="27"/>
+      <x:c r="B8" s="27"/>
+      <x:c r="C8" s="28"/>
+      <x:c r="D8" s="27" t="str">
         <x:v>Section</x:v>
       </x:c>
-      <x:c r="E8" s="16"/>
-      <x:c r="F8" s="15"/>
-      <x:c r="G8" s="15" t="str">
-        <x:v>**Point estimation**</x:v>
-      </x:c>
-      <x:c r="H8" s="15"/>
-      <x:c r="I8" s="15"/>
-      <x:c r="J8" s="15"/>
+      <x:c r="E8" s="27"/>
+      <x:c r="F8" s="29"/>
+      <x:c r="G8" s="29" t="str">
+        <x:v>Point estimation</x:v>
+      </x:c>
+      <x:c r="H8" s="29"/>
+      <x:c r="I8" s="29"/>
+      <x:c r="J8" s="29"/>
     </x:row>
     <x:row r="9" ht="15.75" hidden="0" customHeight="1">
       <x:c r="A9" s="16"/>
@@ -761,21 +816,21 @@
       <x:c r="I18" s="15"/>
       <x:c r="J18" s="15"/>
     </x:row>
-    <x:row r="19" ht="15.75" hidden="0" customHeight="1">
-      <x:c r="A19" s="16"/>
-      <x:c r="B19" s="16"/>
-      <x:c r="C19" s="17"/>
-      <x:c r="D19" s="16" t="str">
+    <x:row r="19" ht="28" hidden="0" customHeight="1">
+      <x:c r="A19" s="27"/>
+      <x:c r="B19" s="27"/>
+      <x:c r="C19" s="28"/>
+      <x:c r="D19" s="27" t="str">
         <x:v>Section</x:v>
       </x:c>
-      <x:c r="E19" s="16"/>
-      <x:c r="F19" s="15"/>
-      <x:c r="G19" s="15" t="str">
-        <x:v>**Hypothesis Testing**</x:v>
-      </x:c>
-      <x:c r="H19" s="15"/>
-      <x:c r="I19" s="15"/>
-      <x:c r="J19" s="15"/>
+      <x:c r="E19" s="27"/>
+      <x:c r="F19" s="29"/>
+      <x:c r="G19" s="29" t="str">
+        <x:v>Hypothesis Testing</x:v>
+      </x:c>
+      <x:c r="H19" s="29"/>
+      <x:c r="I19" s="29"/>
+      <x:c r="J19" s="29"/>
     </x:row>
     <x:row r="20" ht="15.75" hidden="0" customHeight="1">
       <x:c r="A20" s="16"/>
@@ -891,21 +946,21 @@
       <x:c r="I24" s="15"/>
       <x:c r="J24" s="15"/>
     </x:row>
-    <x:row r="25" ht="15.75" hidden="0" customHeight="1">
-      <x:c r="A25" s="16"/>
-      <x:c r="B25" s="16"/>
-      <x:c r="C25" s="17"/>
-      <x:c r="D25" s="16" t="str">
+    <x:row r="25" ht="28" hidden="0" customHeight="1">
+      <x:c r="A25" s="27"/>
+      <x:c r="B25" s="27"/>
+      <x:c r="C25" s="28"/>
+      <x:c r="D25" s="27" t="str">
         <x:v>Section</x:v>
       </x:c>
-      <x:c r="E25" s="16"/>
-      <x:c r="F25" s="15"/>
-      <x:c r="G25" s="15" t="str">
-        <x:v>**Large Sample Theory**</x:v>
-      </x:c>
-      <x:c r="H25" s="15"/>
-      <x:c r="I25" s="15"/>
-      <x:c r="J25" s="15"/>
+      <x:c r="E25" s="27"/>
+      <x:c r="F25" s="29"/>
+      <x:c r="G25" s="29" t="str">
+        <x:v>Large Sample Theory</x:v>
+      </x:c>
+      <x:c r="H25" s="29"/>
+      <x:c r="I25" s="29"/>
+      <x:c r="J25" s="29"/>
     </x:row>
     <x:row r="26" ht="15.75" hidden="0" customHeight="1">
       <x:c r="A26" s="16" t="n">
@@ -1045,21 +1100,21 @@
       </x:c>
       <x:c r="J31" s="15"/>
     </x:row>
-    <x:row r="32" ht="15.75" hidden="0" customHeight="1">
-      <x:c r="A32" s="16"/>
-      <x:c r="B32" s="16"/>
-      <x:c r="C32" s="17"/>
-      <x:c r="D32" s="16" t="str">
+    <x:row r="32" ht="28" hidden="0" customHeight="1">
+      <x:c r="A32" s="27"/>
+      <x:c r="B32" s="27"/>
+      <x:c r="C32" s="28"/>
+      <x:c r="D32" s="27" t="str">
         <x:v>Section</x:v>
       </x:c>
-      <x:c r="E32" s="16"/>
-      <x:c r="F32" s="15"/>
-      <x:c r="G32" s="15" t="str">
-        <x:v>**Confidence intervals**</x:v>
-      </x:c>
-      <x:c r="H32" s="15"/>
-      <x:c r="I32" s="15"/>
-      <x:c r="J32" s="15"/>
+      <x:c r="E32" s="27"/>
+      <x:c r="F32" s="29"/>
+      <x:c r="G32" s="29" t="str">
+        <x:v>Confidence intervals</x:v>
+      </x:c>
+      <x:c r="H32" s="29"/>
+      <x:c r="I32" s="29"/>
+      <x:c r="J32" s="29"/>
     </x:row>
     <x:row r="33" ht="15.75" hidden="0" customHeight="1">
       <x:c r="A33" s="16" t="n">
@@ -1408,7 +1463,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b1aae5080514be1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c6857dd2f3d4eef"/>
   </x:tableParts>
 </x:worksheet>
 </file>